--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU_05/HRM/post DDV_HRM-2031-0200/Panel-28/Coupon back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU05_Coupon_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU_05/HRM/post DDV_HRM-2031-0200/Panel-28/Coupon back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU05_Coupon_Back_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.9643</v>
+        <v>17.02522</v>
       </c>
       <c r="D2" t="n">
-        <v>16.85312</v>
+        <v>16.60859</v>
       </c>
       <c r="E2" t="n">
-        <v>16.99438</v>
+        <v>16.94549</v>
       </c>
       <c r="F2" t="n">
-        <v>42.82346</v>
+        <v>43.19884</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05145</v>
+        <v>0.05164</v>
       </c>
       <c r="H2" t="n">
-        <v>1.83123</v>
+        <v>1.83703</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.88124</v>
+        <v>17.42489</v>
       </c>
       <c r="D3" t="n">
-        <v>16.90298</v>
+        <v>17.07593</v>
       </c>
       <c r="E3" t="n">
-        <v>17.21632</v>
+        <v>17.35656</v>
       </c>
       <c r="F3" t="n">
-        <v>43.05711</v>
+        <v>42.79014</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05121</v>
+        <v>0.05159</v>
       </c>
       <c r="H3" t="n">
-        <v>1.84291</v>
+        <v>1.8438</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.13008</v>
+        <v>17.11666</v>
       </c>
       <c r="D4" t="n">
-        <v>16.8</v>
+        <v>16.81255</v>
       </c>
       <c r="E4" t="n">
-        <v>17.10928</v>
+        <v>17.04568</v>
       </c>
       <c r="F4" t="n">
-        <v>43.4164</v>
+        <v>44.17653</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0523</v>
+        <v>0.05227</v>
       </c>
       <c r="H4" t="n">
-        <v>1.84851</v>
+        <v>1.87036</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.83098</v>
+        <v>16.54086</v>
       </c>
       <c r="D6" t="n">
-        <v>16.3799</v>
+        <v>16.26545</v>
       </c>
       <c r="E6" t="n">
-        <v>17.03788</v>
+        <v>16.48241</v>
       </c>
       <c r="F6" t="n">
-        <v>22.84119</v>
+        <v>22.1029</v>
       </c>
       <c r="G6" t="n">
-        <v>34.82003</v>
+        <v>35.32305</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.07004</v>
+        <v>16.97484</v>
       </c>
       <c r="D7" t="n">
-        <v>16.30269</v>
+        <v>16.135</v>
       </c>
       <c r="E7" t="n">
-        <v>16.52928</v>
+        <v>16.83956</v>
       </c>
       <c r="F7" t="n">
-        <v>22.23276</v>
+        <v>22.75435</v>
       </c>
       <c r="G7" t="n">
-        <v>34.91249</v>
+        <v>34.8682</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.21758</v>
+        <v>17.14927</v>
       </c>
       <c r="D8" t="n">
-        <v>16.54224</v>
+        <v>16.17129</v>
       </c>
       <c r="E8" t="n">
-        <v>16.17941</v>
+        <v>16.30429</v>
       </c>
       <c r="F8" t="n">
-        <v>22.39027</v>
+        <v>21.85222</v>
       </c>
       <c r="G8" t="n">
-        <v>34.4651</v>
+        <v>34.83112</v>
       </c>
     </row>
   </sheetData>
